--- a/output/valuation_model.xlsx
+++ b/output/valuation_model.xlsx
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -1174,28 +1174,28 @@
         </is>
       </c>
       <c r="B2" s="20" t="n">
-        <v>56604.13545082045</v>
+        <v>55945.73141458551</v>
       </c>
       <c r="C2" s="20" t="n">
-        <v>19290.69621770648</v>
+        <v>7525.132373302518</v>
       </c>
       <c r="D2" s="20" t="n">
-        <v>0.0148</v>
+        <v>0</v>
       </c>
       <c r="E2" s="20" t="n">
-        <v>0.2798</v>
+        <v>0.2386</v>
       </c>
       <c r="F2" s="20" t="n">
-        <v>17698.21735012726</v>
+        <v>22618.96008878888</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>-230892.6734273678</v>
+        <v>-68984.74517214198</v>
       </c>
       <c r="H2" s="20" t="n">
-        <v>54599.53774732679</v>
+        <v>32119.7289792505</v>
       </c>
       <c r="I2" s="20" t="n">
-        <v>135181.3123200588</v>
+        <v>86879.89053237437</v>
       </c>
     </row>
     <row r="3">
@@ -1205,28 +1205,28 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
-        <v>56599.80724727189</v>
+        <v>55944.8657738758</v>
       </c>
       <c r="C3" s="20" t="n">
-        <v>14971.28376368536</v>
+        <v>7216.441336315943</v>
       </c>
       <c r="D3" s="20" t="n">
-        <v>0.0056</v>
+        <v>0</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>0.2764</v>
+        <v>0.2402</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>17774.27329475762</v>
+        <v>22621.46287386537</v>
       </c>
       <c r="G3" s="20" t="n">
-        <v>-229773.2852887917</v>
+        <v>-68315.13052979074</v>
       </c>
       <c r="H3" s="20" t="n">
-        <v>54621.42506539929</v>
+        <v>32067.12687176187</v>
       </c>
       <c r="I3" s="20" t="n">
-        <v>133938.7551344922</v>
+        <v>86680.68610460378</v>
       </c>
     </row>
     <row r="4">
@@ -1236,28 +1236,28 @@
         </is>
       </c>
       <c r="B4" s="20" t="n">
-        <v>56595.47904372337</v>
+        <v>55944.00013316609</v>
       </c>
       <c r="C4" s="20" t="n">
-        <v>10993.27122828938</v>
+        <v>7022.435887719657</v>
       </c>
       <c r="D4" s="20" t="n">
-        <v>0.0004</v>
+        <v>0</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>0.275</v>
+        <v>0.2398</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>17820.33645207124</v>
+        <v>22620.62065783985</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>-228161.979569602</v>
+        <v>-67433.63953206291</v>
       </c>
       <c r="H4" s="20" t="n">
-        <v>54300.23818776359</v>
+        <v>31934.46492287031</v>
       </c>
       <c r="I4" s="20" t="n">
-        <v>132924.9602123474</v>
+        <v>86330.39544416311</v>
       </c>
     </row>
     <row r="5">
@@ -1267,28 +1267,28 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>56591.15084017482</v>
+        <v>55943.13449245637</v>
       </c>
       <c r="C5" s="20" t="n">
-        <v>7891.069944036331</v>
+        <v>6952.723059755523</v>
       </c>
       <c r="D5" s="20" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>0.274</v>
+        <v>0.2396</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>17834.51285073023</v>
+        <v>22618.34320955404</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>-225554.1124098116</v>
+        <v>-66944.9490826847</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>54233.9002120279</v>
+        <v>31780.08328281715</v>
       </c>
       <c r="I5" s="20" t="n">
-        <v>132013.4288144633</v>
+        <v>85981.5371078693</v>
       </c>
     </row>
   </sheetData>
@@ -4276,7 +4276,7 @@
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>270293.8804579086</v>
+        <v>263454.583094678</v>
       </c>
     </row>
     <row r="4">
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>25367.9972934622</v>
+        <v>23510.60630821528</v>
       </c>
     </row>
     <row r="5">
@@ -4306,7 +4306,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>0.08751626610653301</v>
+        <v>0.08590931550847444</v>
       </c>
     </row>
   </sheetData>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>8.59%</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5967,7 +5967,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>83</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -6064,13 +6064,13 @@
         </is>
       </c>
       <c r="D2" s="26" t="n">
-        <v>732270.8</v>
+        <v>714731.2</v>
       </c>
       <c r="E2" s="26" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="F2" s="26" t="n">
-        <v>150830</v>
+        <v>146066.6</v>
       </c>
     </row>
     <row r="3">
@@ -6090,13 +6090,13 @@
         </is>
       </c>
       <c r="D3" s="26" t="n">
-        <v>270293.9</v>
+        <v>263454.6</v>
       </c>
       <c r="E3" s="26" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="F3" s="26" t="n">
-        <v>25368</v>
+        <v>23510.6</v>
       </c>
     </row>
     <row r="4">
@@ -6116,13 +6116,13 @@
         </is>
       </c>
       <c r="D4" s="26" t="n">
-        <v>1085586.1</v>
+        <v>1068181.2</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="F4" s="26" t="n">
-        <v>246782</v>
+        <v>242055.3</v>
       </c>
     </row>
     <row r="5">
@@ -6142,13 +6142,13 @@
         </is>
       </c>
       <c r="D5" s="26" t="n">
-        <v>416123.5</v>
+        <v>409320.1</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>64971.9</v>
+        <v>63124.2</v>
       </c>
     </row>
   </sheetData>
@@ -6212,19 +6212,19 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>33077.6763671701</v>
+        <v>31037.74311523229</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>36323.37133260326</v>
+        <v>34209.28175998493</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>39869.59360965054</v>
+        <v>37674.48139036282</v>
       </c>
       <c r="E2" s="14" t="n">
-        <v>43760.10931165389</v>
+        <v>41476.10816932104</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>48047.6164118208</v>
+        <v>45665.65604817297</v>
       </c>
     </row>
     <row r="3">
@@ -6234,19 +6234,19 @@
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>26348.55612065448</v>
+        <v>24465.60698770484</v>
       </c>
       <c r="C3" s="14" t="n">
-        <v>29058.44933274219</v>
+        <v>27113.6318997017</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>31997.99451195593</v>
+        <v>29986.06570254579</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>35197.67643269305</v>
+        <v>33112.69718705742</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>38693.62519794283</v>
+        <v>36528.83158680164</v>
       </c>
     </row>
     <row r="4">
@@ -6256,19 +6256,19 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>20605.50795939226</v>
+        <v>18856.76675187097</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>22897.23215022291</v>
+        <v>21096.20834289379</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>25367.9972934622</v>
+        <v>23510.60630821528</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>28039.63765159898</v>
+        <v>26121.29679104252</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>30937.68820957785</v>
+        <v>28953.23223004157</v>
       </c>
     </row>
     <row r="5">
@@ -6278,19 +6278,19 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>15648.3617377228</v>
+        <v>14015.6698203075</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>17607.87239457286</v>
+        <v>15930.50959679754</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>19709.37657728159</v>
+        <v>17984.10587883035</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>21968.88859327671</v>
+        <v>20192.10789635429</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>24404.92498552141</v>
+        <v>22572.61007149731</v>
       </c>
     </row>
     <row r="6">
@@ -6300,19 +6300,19 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>11327.63225740868</v>
+        <v>9796.279527358967</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>13019.14563526572</v>
+        <v>11449.25948475747</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>14824.95045757255</v>
+        <v>13213.92727711535</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>16757.03533738335</v>
+        <v>15101.99841159608</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>18829.12636790505</v>
+        <v>17126.88629495226</v>
       </c>
     </row>
   </sheetData>
@@ -6376,19 +6376,19 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>93773.52061377498</v>
+        <v>66842.60791356159</v>
       </c>
       <c r="C2" s="14" t="n">
-        <v>81902.64301997662</v>
+        <v>53475.56850308477</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>70031.76542617832</v>
+        <v>40108.52909260783</v>
       </c>
       <c r="E2" s="14" t="n">
-        <v>58160.88783238004</v>
+        <v>26741.48968213108</v>
       </c>
       <c r="F2" s="14" t="n">
-        <v>46290.01023858162</v>
+        <v>13374.45027165417</v>
       </c>
     </row>
     <row r="3">
@@ -6398,19 +6398,19 @@
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>73674.82495405276</v>
+        <v>59373.54266058495</v>
       </c>
       <c r="C3" s="14" t="n">
-        <v>60687.35315693651</v>
+        <v>45591.5551804982</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>47699.8813598202</v>
+        <v>31809.56770041155</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>34712.40956270398</v>
+        <v>18027.58022032489</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>21724.93776558769</v>
+        <v>4245.592740238215</v>
       </c>
     </row>
     <row r="4">
@@ -6420,19 +6420,19 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>53576.12929433053</v>
+        <v>51904.47740760828</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>39472.06329389635</v>
+        <v>37707.54185791176</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>25367.9972934622</v>
+        <v>23510.60630821528</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>11263.93129302805</v>
+        <v>9313.670758518807</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>-2840.134707406078</v>
+        <v>-4883.264791177713</v>
       </c>
     </row>
     <row r="5">
@@ -6442,19 +6442,19 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>33477.43363460839</v>
+        <v>44435.41215463159</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>18256.77343085625</v>
+        <v>29823.52853532525</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>3036.113227104134</v>
+        <v>15211.64491601889</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>-12184.54697664784</v>
+        <v>599.7612967126743</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>-27405.20718039997</v>
+        <v>-14012.12232259366</v>
       </c>
     </row>
     <row r="6">
@@ -6464,19 +6464,19 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>13378.73797488605</v>
+        <v>36966.34690165488</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>-2958.516432183975</v>
+        <v>21939.51521273876</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>-19295.77083925386</v>
+        <v>6912.683523822717</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>-35633.02524632378</v>
+        <v>-8114.148165093371</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>-51970.2796533938</v>
+        <v>-23140.97985400953</v>
       </c>
     </row>
   </sheetData>
